--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,45 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-06-12</t>
+    <t>2026-06-23</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
     <t>2026-06-24</t>
   </si>
   <si>
@@ -293,6 +260,36 @@
   </si>
   <si>
     <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
   </si>
   <si>
     <t>Reason</t>
@@ -369,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -418,11 +415,11 @@
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+      <c r="B4" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -436,7 +433,7 @@
         <v>18.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>0.0</v>
@@ -447,7 +444,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
@@ -461,7 +458,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -475,7 +472,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>0.0</v>
@@ -489,7 +486,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>0.0</v>
@@ -503,7 +500,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -517,7 +514,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -531,7 +528,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -545,7 +542,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -559,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -573,7 +570,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -587,7 +584,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -601,7 +598,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -615,7 +612,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -629,7 +626,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -643,7 +640,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -657,7 +654,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -671,7 +668,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -825,7 +822,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -839,7 +836,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -853,7 +850,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -867,7 +864,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -881,7 +878,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -895,7 +892,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -909,7 +906,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -923,7 +920,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -937,7 +934,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -951,7 +948,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -965,7 +962,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -979,7 +976,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -993,7 +990,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1007,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1021,7 +1018,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1035,7 +1032,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1049,7 +1046,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1063,7 +1060,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1077,7 +1074,7 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1091,7 +1088,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1105,7 +1102,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1119,7 +1116,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1133,7 +1130,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1147,7 +1144,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -1161,7 +1158,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1175,7 +1172,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1189,7 +1186,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1203,7 +1200,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1217,7 +1214,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1231,7 +1228,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1245,7 +1242,7 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1259,7 +1256,7 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1273,7 +1270,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>0.0</v>
@@ -1287,7 +1284,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1301,7 +1298,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1315,7 +1312,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1329,7 +1326,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1343,7 +1340,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1357,7 +1354,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1371,7 +1368,7 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1385,7 +1382,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1399,7 +1396,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1413,7 +1410,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1427,7 +1424,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1441,7 +1438,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1455,7 +1452,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1525,7 +1522,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1539,7 +1536,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1553,7 +1550,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1567,7 +1564,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1581,7 +1578,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1595,26 +1592,12 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>12.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1630,24 +1613,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
-      </c>
       <c r="C2" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
   </sheetData>
@@ -1662,18 +1645,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,27 +28,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>2026-06-27</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
     <t>2026-06-29</t>
   </si>
   <si>
@@ -290,6 +269,27 @@
   </si>
   <si>
     <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -387,11 +387,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -399,13 +399,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -413,10 +413,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -427,10 +427,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
@@ -441,10 +441,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
@@ -455,10 +455,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>0.0</v>
@@ -483,10 +483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>0.0</v>
@@ -497,10 +497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -525,7 +525,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>17.0</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>17.0</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>17.0</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>17.0</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>17.0</v>
@@ -595,7 +595,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
         <v>17.0</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>17.0</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>17.0</v>
@@ -637,7 +637,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>17.0</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
         <v>17.0</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>17.0</v>
@@ -679,7 +679,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>17.0</v>
@@ -693,7 +693,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
         <v>17.0</v>
@@ -707,7 +707,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
         <v>17.0</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>17.0</v>
@@ -735,10 +735,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -749,10 +749,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -763,10 +763,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -805,10 +805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>16.0</v>
@@ -833,10 +833,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -847,10 +847,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -861,10 +861,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -875,10 +875,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -917,10 +917,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -945,10 +945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -959,10 +959,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -987,10 +987,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>13.0</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1309,10 +1309,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>13.0</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>13.0</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>13.0</v>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>13.0</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1589,15 +1589,29 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="B88" t="n" s="0">
-        <v>13.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
+      <c r="B89" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1630,7 +1644,7 @@
         <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
   <si>
     <t>Date</t>
   </si>
@@ -28,36 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>2026-07-05</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
     <t>2026-07-08</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-07-09</t>
   </si>
   <si>
@@ -290,6 +266,27 @@
   </si>
   <si>
     <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -387,11 +384,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>18.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>0.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -399,10 +396,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -413,10 +410,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -427,10 +424,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
@@ -441,7 +438,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>17.0</v>
@@ -455,7 +452,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>17.0</v>
@@ -469,7 +466,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>17.0</v>
@@ -483,7 +480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>17.0</v>
@@ -497,7 +494,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
         <v>17.0</v>
@@ -511,7 +508,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>17.0</v>
@@ -525,7 +522,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>17.0</v>
@@ -539,7 +536,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>17.0</v>
@@ -553,7 +550,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>17.0</v>
@@ -567,7 +564,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>17.0</v>
@@ -581,7 +578,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>17.0</v>
@@ -595,7 +592,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
         <v>17.0</v>
@@ -609,10 +606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -623,10 +620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -637,10 +634,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -651,10 +648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -665,10 +662,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -679,10 +676,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -693,10 +690,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -707,10 +704,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -721,10 +718,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -735,10 +732,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -749,10 +746,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -763,10 +760,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -777,10 +774,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -791,10 +788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -805,10 +802,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -819,10 +816,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -833,10 +830,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -847,10 +844,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -861,10 +858,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -875,10 +872,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -889,10 +886,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -903,10 +900,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -917,10 +914,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -931,10 +928,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -945,10 +942,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -959,10 +956,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -973,10 +970,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -987,10 +984,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1001,10 +998,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1015,10 +1012,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1029,10 +1026,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1043,10 +1040,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1057,10 +1054,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1071,10 +1068,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1085,10 +1082,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1099,10 +1096,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1113,10 +1110,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1127,10 +1124,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1141,10 +1138,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -1155,10 +1152,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1169,10 +1166,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1183,10 +1180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1197,10 +1194,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1211,10 +1208,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1225,10 +1222,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1239,10 +1236,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1253,7 +1250,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>13.0</v>
@@ -1267,7 +1264,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>13.0</v>
@@ -1281,10 +1278,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1295,10 +1292,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1309,10 +1306,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1323,10 +1320,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1337,10 +1334,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1351,10 +1348,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1365,10 +1362,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1379,7 +1376,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>13.0</v>
@@ -1393,10 +1390,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1407,10 +1404,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1421,10 +1418,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1435,10 +1432,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1449,10 +1446,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1463,10 +1460,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1477,10 +1474,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1491,10 +1488,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1505,10 +1502,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1519,10 +1516,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1533,10 +1530,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1547,10 +1544,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1561,10 +1558,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1575,43 +1572,15 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1627,24 +1596,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>96</v>
-      </c>
       <c r="C2" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
   </sheetData>
@@ -1659,18 +1628,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>97</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -28,265 +28,274 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-07-08</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>2026-10-11</t>
+  </si>
+  <si>
+    <t>2026-10-12</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>2026-07-12</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>2026-07-19</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
-    <t>2026-07-22</t>
-  </si>
-  <si>
-    <t>2026-07-23</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>2026-07-26</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>2026-07-28</t>
-  </si>
-  <si>
-    <t>2026-07-29</t>
-  </si>
-  <si>
-    <t>2026-07-30</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-01</t>
-  </si>
-  <si>
-    <t>2026-08-02</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>2026-08-09</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>2026-08-11</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>2026-08-15</t>
-  </si>
-  <si>
-    <t>2026-08-16</t>
-  </si>
-  <si>
-    <t>2026-08-17</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-08-19</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>2026-08-22</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-08-29</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
-    <t>2026-09-03</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>2026-09-06</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>2026-09-13</t>
-  </si>
-  <si>
-    <t>2026-09-14</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-16</t>
-  </si>
-  <si>
-    <t>2026-09-17</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>2026-09-19</t>
-  </si>
-  <si>
-    <t>2026-09-20</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>2026-09-22</t>
-  </si>
-  <si>
-    <t>2026-09-23</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>2026-09-26</t>
-  </si>
-  <si>
-    <t>2026-09-27</t>
-  </si>
-  <si>
-    <t>2026-09-28</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>2026-10-01</t>
   </si>
   <si>
     <t>Reason</t>
@@ -363,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -384,11 +393,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -396,7 +405,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n" s="0">
         <v>17.0</v>
@@ -410,7 +419,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
         <v>17.0</v>
@@ -424,7 +433,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>17.0</v>
@@ -438,7 +447,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>17.0</v>
@@ -452,7 +461,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>17.0</v>
@@ -466,7 +475,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>17.0</v>
@@ -480,7 +489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>17.0</v>
@@ -494,10 +503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -508,10 +517,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -522,10 +531,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -536,10 +545,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -550,10 +559,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -564,10 +573,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -578,10 +587,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -592,10 +601,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -606,10 +615,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -620,10 +629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -634,10 +643,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -648,10 +657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -662,10 +671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -676,10 +685,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -690,10 +699,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -704,10 +713,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -718,10 +727,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -732,10 +741,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -746,10 +755,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -760,10 +769,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -774,10 +783,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -788,10 +797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -802,10 +811,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -816,10 +825,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -830,10 +839,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -844,10 +853,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -858,10 +867,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -872,10 +881,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -886,10 +895,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -900,10 +909,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -914,10 +923,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -928,10 +937,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -942,10 +951,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -956,10 +965,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -970,10 +979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -984,10 +993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -998,10 +1007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1012,10 +1021,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1026,10 +1035,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1040,10 +1049,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1054,10 +1063,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1068,10 +1077,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1082,10 +1091,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1096,10 +1105,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1110,10 +1119,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1124,10 +1133,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1138,7 +1147,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>13.0</v>
@@ -1152,10 +1161,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1166,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1180,10 +1189,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1194,10 +1203,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1208,10 +1217,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1222,10 +1231,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1236,10 +1245,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1250,7 +1259,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>13.0</v>
@@ -1264,7 +1273,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>13.0</v>
@@ -1278,10 +1287,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1292,10 +1301,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1306,10 +1315,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1320,10 +1329,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1334,10 +1343,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1348,10 +1357,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1362,10 +1371,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1376,10 +1385,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1390,10 +1399,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1404,10 +1413,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1418,10 +1427,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1432,10 +1441,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1446,10 +1455,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1460,10 +1469,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1474,10 +1483,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1488,10 +1497,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1502,10 +1511,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1516,10 +1525,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1530,7 +1539,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
         <v>11.0</v>
@@ -1544,10 +1553,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1558,10 +1567,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1572,16 +1581,58 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B87" t="n" s="0">
-        <v>13.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
-        <v>0.0</v>
+      <c r="B88" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1596,24 +1647,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>
@@ -1628,18 +1679,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -28,27 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>2026-07-19</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
     <t>2026-07-22</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-07-23</t>
   </si>
   <si>
@@ -295,7 +280,25 @@
     <t>2026-10-12</t>
   </si>
   <si>
-    <t/>
+    <t>2026-10-13</t>
+  </si>
+  <si>
+    <t>2026-10-14</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>2026-10-17</t>
+  </si>
+  <si>
+    <t>2026-10-18</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
   </si>
   <si>
     <t>Reason</t>
@@ -372,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -393,11 +396,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>0.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -405,7 +408,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n" s="0">
         <v>17.0</v>
@@ -419,10 +422,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -433,10 +436,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
@@ -447,10 +450,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
@@ -461,10 +464,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -475,10 +478,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>0.0</v>
@@ -489,10 +492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>0.0</v>
@@ -503,7 +506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
         <v>16.0</v>
@@ -517,10 +520,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -531,10 +534,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -545,10 +548,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -559,10 +562,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -573,10 +576,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -587,10 +590,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -601,10 +604,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -615,10 +618,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -629,10 +632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -643,10 +646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -657,10 +660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -671,10 +674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -685,10 +688,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -699,10 +702,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -713,10 +716,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -727,10 +730,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -741,10 +744,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -755,10 +758,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -769,10 +772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -783,10 +786,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -797,10 +800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -811,10 +814,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -825,10 +828,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -839,10 +842,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -853,10 +856,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -867,10 +870,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -881,10 +884,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -895,10 +898,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -909,10 +912,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -923,10 +926,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -937,10 +940,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -951,7 +954,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>13.0</v>
@@ -965,10 +968,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -979,10 +982,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -993,10 +996,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1007,10 +1010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1021,10 +1024,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1035,10 +1038,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1049,10 +1052,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1063,10 +1066,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1077,10 +1080,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1091,10 +1094,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1105,10 +1108,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1133,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1147,7 +1150,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>13.0</v>
@@ -1161,7 +1164,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>13.0</v>
@@ -1175,7 +1178,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>13.0</v>
@@ -1189,7 +1192,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>13.0</v>
@@ -1203,10 +1206,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1217,10 +1220,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1231,10 +1234,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1245,10 +1248,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1259,10 +1262,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1273,10 +1276,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>0.0</v>
@@ -1287,7 +1290,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>10.0</v>
@@ -1301,10 +1304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1315,10 +1318,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1329,10 +1332,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1343,10 +1346,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1357,10 +1360,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1371,10 +1374,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1385,10 +1388,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1399,10 +1402,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1413,10 +1416,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1427,10 +1430,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1441,7 +1444,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>13.0</v>
@@ -1455,10 +1458,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1469,10 +1472,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1483,10 +1486,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1497,10 +1500,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1511,10 +1514,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1525,10 +1528,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1539,10 +1542,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1553,10 +1556,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1567,10 +1570,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1581,10 +1584,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1595,10 +1598,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>0.0</v>
@@ -1609,10 +1612,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>0.0</v>
@@ -1623,16 +1626,30 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B90" t="n" s="0">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="C90" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>93</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D91" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1647,24 +1664,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
     </row>
   </sheetData>
@@ -1679,18 +1696,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
   <si>
     <t>Date</t>
   </si>
@@ -28,16 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-07-22</t>
+    <t>2026-07-24</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2026-07-23</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
   </si>
   <si>
     <t>2026-07-25</t>
@@ -375,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -410,11 +404,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>0.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -424,11 +418,11 @@
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>0.0</v>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -495,7 +489,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>0.0</v>
@@ -509,7 +503,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -551,7 +545,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -565,7 +559,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -593,7 +587,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -607,7 +601,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -649,7 +643,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -663,7 +657,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -691,7 +685,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -705,7 +699,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -747,7 +741,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -761,7 +755,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -789,7 +783,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -803,7 +797,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -845,7 +839,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -859,7 +853,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -943,7 +937,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -957,7 +951,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -985,7 +979,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -999,7 +993,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1041,7 +1035,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1055,7 +1049,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1181,7 +1175,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1195,7 +1189,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1279,7 +1273,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>0.0</v>
@@ -1293,7 +1287,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1335,7 +1329,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1349,7 +1343,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1433,7 +1427,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1447,7 +1441,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1475,7 +1469,7 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1489,7 +1483,7 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1531,7 +1525,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1545,7 +1539,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1573,7 +1567,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1587,7 +1581,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1622,34 +1616,6 @@
       </c>
       <c r="D89" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>14.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>14.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D91" t="s" s="0">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1664,21 +1630,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>14.0</v>
@@ -1696,18 +1662,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,18 +28,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>2026-07-26</t>
-  </si>
-  <si>
     <t>2026-07-27</t>
   </si>
   <si>
@@ -293,6 +281,15 @@
   </si>
   <si>
     <t>2026-10-19</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
+  </si>
+  <si>
+    <t>2026-10-22</t>
   </si>
   <si>
     <t>Reason</t>
@@ -390,11 +387,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -402,13 +399,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -416,13 +413,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -430,7 +427,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>16.0</v>
@@ -444,10 +441,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
@@ -458,10 +455,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -472,10 +469,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>0.0</v>
@@ -486,7 +483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>14.0</v>
@@ -500,10 +497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -514,10 +511,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -528,10 +525,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -542,10 +539,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -556,10 +553,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -570,10 +567,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -584,7 +581,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>4.0</v>
@@ -598,10 +595,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -612,10 +609,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -626,10 +623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -640,10 +637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -654,10 +651,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -668,10 +665,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -682,7 +679,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>5.0</v>
@@ -696,10 +693,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -710,10 +707,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -724,10 +721,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -738,10 +735,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -752,10 +749,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -766,10 +763,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -780,7 +777,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>9.0</v>
@@ -794,10 +791,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -808,10 +805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -822,10 +819,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -836,7 +833,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>13.0</v>
@@ -850,7 +847,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>13.0</v>
@@ -864,7 +861,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
         <v>13.0</v>
@@ -878,7 +875,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>13.0</v>
@@ -892,10 +889,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -906,10 +903,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -920,10 +917,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -934,10 +931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -948,10 +945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -962,10 +959,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -976,7 +973,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>12.0</v>
@@ -990,10 +987,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1004,10 +1001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1018,10 +1015,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1032,7 +1029,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>13.0</v>
@@ -1046,7 +1043,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>13.0</v>
@@ -1060,7 +1057,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>13.0</v>
@@ -1074,7 +1071,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>13.0</v>
@@ -1088,7 +1085,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>13.0</v>
@@ -1102,7 +1099,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>13.0</v>
@@ -1116,7 +1113,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>13.0</v>
@@ -1130,10 +1127,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1144,10 +1141,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -1158,10 +1155,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1172,7 +1169,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>10.0</v>
@@ -1186,7 +1183,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>10.0</v>
@@ -1200,7 +1197,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>10.0</v>
@@ -1214,7 +1211,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>10.0</v>
@@ -1228,10 +1225,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1242,10 +1239,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1256,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1270,7 +1267,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>11.0</v>
@@ -1284,10 +1281,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1298,10 +1295,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1312,10 +1309,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1326,7 +1323,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>13.0</v>
@@ -1340,7 +1337,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>13.0</v>
@@ -1354,7 +1351,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>13.0</v>
@@ -1368,7 +1365,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>13.0</v>
@@ -1382,10 +1379,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1396,10 +1393,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1410,10 +1407,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1424,10 +1421,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1438,10 +1435,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1452,10 +1449,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1466,7 +1463,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>9.0</v>
@@ -1480,10 +1477,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1494,10 +1491,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1508,10 +1505,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1522,10 +1519,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1536,10 +1533,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1550,10 +1547,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1564,7 +1561,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
         <v>14.0</v>
@@ -1578,10 +1575,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1592,10 +1589,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>0.0</v>
@@ -1606,10 +1603,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>0.0</v>
@@ -1630,24 +1627,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
-      </c>
       <c r="C2" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
   </sheetData>
@@ -1662,18 +1659,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>101</v>
       </c>
     </row>
   </sheetData>
